--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-specimen)
 </t>
   </si>
   <si>
@@ -709,7 +709,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -1434,7 +1434,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="59.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="120.3125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
